--- a/output/pdf_financials_xlsx/GRBM.xlsx
+++ b/output/pdf_financials_xlsx/GRBM.xlsx
@@ -601,16 +601,16 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.436763</v>
+        <v>0.59067</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.471101</v>
+        <v>0.567706</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.505871</v>
+        <v>4.431966</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.367176</v>
+        <v>2.116224</v>
       </c>
     </row>
     <row r="11">
@@ -639,16 +639,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.019819</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.028979</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.062208</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.018709</v>
       </c>
     </row>
     <row r="13">
@@ -942,16 +942,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.539</v>
+        <v>-0.558819</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.539</v>
+        <v>-0.567979</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-4.337531</v>
+        <v>-4.399739</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.116719</v>
+        <v>-2.135428</v>
       </c>
     </row>
     <row r="28">
@@ -980,16 +980,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.539</v>
+        <v>-0.558819</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.539</v>
+        <v>-0.567979</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-4.325624</v>
+        <v>-4.387832</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.044933</v>
+        <v>-2.063642</v>
       </c>
     </row>
     <row r="30">
@@ -1085,10 +1085,10 @@
         <v>1.109048</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.953916</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>4.315301</v>
       </c>
     </row>
     <row r="35">
@@ -1123,10 +1123,10 @@
         <v>1.109048</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.953916</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>4.315301</v>
       </c>
     </row>
     <row r="37">
@@ -1351,10 +1351,10 @@
         <v>0.016485</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.042896</v>
+        <v>0.08898</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>4.36233</v>
+        <v>0.047029</v>
       </c>
     </row>
     <row r="49">
@@ -2797,10 +2797,10 @@
         <v>0</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.013973</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-0.084914</v>
       </c>
     </row>
     <row r="125">
@@ -2816,10 +2816,10 @@
         <v>0</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.013973</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-0.084914</v>
       </c>
     </row>
     <row r="126">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -4790,7 +4790,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -6066,20 +6070,20 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>-0.59067</v>
+        <v>0.59067</v>
       </c>
       <c r="F86" s="5" t="n">
-        <v>-0.567706</v>
+        <v>0.567706</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>-4.431966</v>
+        <v>4.431966</v>
       </c>
       <c r="H86" s="5" t="n">
-        <v>-2.116224</v>
+        <v>2.116224</v>
       </c>
     </row>
     <row r="87">
@@ -6202,7 +6206,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E90" s="5" t="n">

--- a/output/pdf_financials_xlsx/GRBM.xlsx
+++ b/output/pdf_financials_xlsx/GRBM.xlsx
@@ -1657,16 +1657,16 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.168913</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.275616</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.667897</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.174554</v>
       </c>
     </row>
     <row r="65">
@@ -1714,16 +1714,16 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.00975</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.0224</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.028175</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.079819</v>
       </c>
     </row>
     <row r="68">
@@ -1777,10 +1777,10 @@
         <v>0</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>0.287535</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0</v>
+        <v>0.222123</v>
       </c>
     </row>
     <row r="71">
@@ -1796,10 +1796,10 @@
         <v>0</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0</v>
+        <v>0.287535</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0.008696000000000001</v>
+        <v>0.230819</v>
       </c>
     </row>
     <row r="72">
@@ -1872,10 +1872,10 @@
         <v>0.12</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0.07424600000000001</v>
+        <v>0</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>0.06514</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -1970,13 +1970,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D80" s="3" t="n">
+        <v>0.08806495983348407</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>0.0007257991552819583</v>
+        <v>0.01926497645158996</v>
       </c>
     </row>
     <row r="81">
@@ -3558,7 +3556,11 @@
           <t>Lease obligations 10</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -3898,7 +3900,11 @@
           <t>Lease obligations 9</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -5186,7 +5192,11 @@
           <t>Fair value of brokers warrants issued for private placement</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -5256,7 +5266,11 @@
           <t>Fair value  of administrative fee shares issued  for  private placement</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -5360,7 +5374,11 @@
           <t>Fair value of brokers’ warrants issued for private placement</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
